--- a/data/raw/workbook.xlsx
+++ b/data/raw/workbook.xlsx
@@ -7,11 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_registry" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_figure_specs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_table_specs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_source_specs" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data_example" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropdowns" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example Indicator" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example Trend" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,129 +416,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>object_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>object_type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>caption</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>data_sheet</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>section_tag</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>order_index</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>CHA Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>fig-example</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>figure</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>fig-example</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Example Indicator by Year</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>data_example</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>example</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
+          <t>One sheet per indicator. Copy an example sheet to add a new indicator.</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tbl-example</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>table</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>tbl-example</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Example Indicator by Year</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>data_example</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>example</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
+          <t>Sheets named Master / Dropdowns and sheets starting with _ are ignored by the build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>See scripts/WORKBOOK_SCHEMA.md for the full schema.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -565,100 +458,137 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>object_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>figure_type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>x_col</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>y_cols</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>x_axis_title</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>y_axis_title</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>start_at_zero</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>hover_suffix</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>pivot_for_chart</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Table/Figure/Both</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Table</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>fig-example</t>
-        </is>
-      </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Figure</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Figure Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
           <t>line</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Region,State</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Percent</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>clustered_bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>stacked_bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>simple_bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>horizontal_bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Format codes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>percent1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>percent2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>currency2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>date</t>
         </is>
       </c>
     </row>
@@ -673,50 +603,334 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>object_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>has_multilevel_headers</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>format_rules_json</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>row_label_col</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Example Indicator</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tbl-example</t>
+          <t>Table/Figure/Both</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Object ID</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>example</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Table Rules</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>percent1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Multilevel Headers</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Enter Data</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Figure Rules</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dutchess</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>62.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Figure Type</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>simple_bar</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>X Column</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Putnam</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>61.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Y Column</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rockland</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>X Axis Title</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>County</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Sullivan</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>55.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Y Axis Title</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ulster</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>60.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Start at Zero</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Westchester</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>66.40000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Hover Suffix</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mid-Hudson</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Show Data Labels</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>{"Region":"percent1","State":"percent1"}</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Year</t>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NYS excl NYC</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Source Specification</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NYS</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://example.org/data</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Year</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Estimate Type</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5-Year Estimates</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Citation Month</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Citation Year</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Custom Text</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Example Data Source, replace with your real citation, accessed Month Year.</t>
         </is>
       </c>
     </row>
@@ -731,203 +945,245 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>object_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>table_id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>data_year</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>estimate_type</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>citation_month</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>citation_year</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>custom_text</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Example Trend</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>fig-example</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://example.org/data</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>5-Year Estimates</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>2025</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Example Data Source, replace with your real citation, accessed Month Year.</t>
+          <t>Table/Figure/Both</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Figure</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tbl-example</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
+          <t>Object ID</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>example-trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Figure Rules</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>percent1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>percent1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Figure Type</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Enter Data</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>X Column</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G6" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Y Column</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G7" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>59.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>X Axis Title</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G8" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Y Axis Title</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G9" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Start at Zero</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G10" t="n">
+        <v>66</v>
+      </c>
+      <c r="H10" t="n">
+        <v>61.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Hover Suffix</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Source Specification</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://example.org/data</t>
         </is>
       </c>
-      <c r="D3" t="n">
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Year</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
         <v>2023</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>5-Year Estimates</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>2025</v>
-      </c>
-      <c r="H3" t="inlineStr">
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Custom Text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Example Data Source, replace with your real citation, accessed Month Year.</t>
         </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Region</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B2" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>58.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B3" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="C3" t="n">
-        <v>59.1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B4" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="C4" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B5" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="C5" t="n">
-        <v>60.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B6" t="n">
-        <v>66</v>
-      </c>
-      <c r="C6" t="n">
-        <v>61.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/workbook.xlsx
+++ b/data/raw/workbook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Work Drive/GitHub/Orange County CHA/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42E6EF7-BB5D-874E-89F4-E4888F087A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA1F964-AC33-2B48-A596-B42D701C24AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" firstSheet="23" activeTab="31" xr2:uid="{7B5489DC-BB92-4237-A1A8-C16ED0406E77}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" firstSheet="17" activeTab="20" xr2:uid="{7B5489DC-BB92-4237-A1A8-C16ED0406E77}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
@@ -5682,11 +5682,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -18126,26 +18126,26 @@
       <c r="G10" s="24">
         <v>113465</v>
       </c>
-      <c r="H10" s="60">
+      <c r="H10" s="59">
         <v>26215</v>
       </c>
-      <c r="I10" s="60"/>
-      <c r="J10" s="60">
+      <c r="I10" s="59"/>
+      <c r="J10" s="59">
         <v>21762</v>
       </c>
-      <c r="K10" s="60"/>
-      <c r="L10" s="60">
+      <c r="K10" s="59"/>
+      <c r="L10" s="59">
         <v>6666</v>
       </c>
-      <c r="M10" s="60"/>
-      <c r="N10" s="60">
+      <c r="M10" s="59"/>
+      <c r="N10" s="59">
         <v>6666</v>
       </c>
-      <c r="O10" s="60"/>
-      <c r="P10" s="60">
+      <c r="O10" s="59"/>
+      <c r="P10" s="59">
         <v>4602</v>
       </c>
-      <c r="Q10" s="60"/>
+      <c r="Q10" s="59"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -18204,7 +18204,7 @@
         <v>1312</v>
       </c>
       <c r="O12" s="54"/>
-      <c r="P12" s="59" t="s">
+      <c r="P12" s="60" t="s">
         <v>1322</v>
       </c>
       <c r="Q12" s="54"/>
@@ -18220,26 +18220,26 @@
       <c r="G13" s="15">
         <v>173986</v>
       </c>
-      <c r="H13" s="60">
+      <c r="H13" s="59">
         <v>43166</v>
       </c>
-      <c r="I13" s="60"/>
-      <c r="J13" s="60">
+      <c r="I13" s="59"/>
+      <c r="J13" s="59">
         <v>32584</v>
       </c>
-      <c r="K13" s="60"/>
-      <c r="L13" s="60">
+      <c r="K13" s="59"/>
+      <c r="L13" s="59">
         <v>11174</v>
       </c>
-      <c r="M13" s="60"/>
-      <c r="N13" s="60">
+      <c r="M13" s="59"/>
+      <c r="N13" s="59">
         <v>10820</v>
       </c>
-      <c r="O13" s="60"/>
-      <c r="P13" s="60">
+      <c r="O13" s="59"/>
+      <c r="P13" s="59">
         <v>6574</v>
       </c>
-      <c r="Q13" s="60"/>
+      <c r="Q13" s="59"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -18490,51 +18490,6 @@
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
     <mergeCell ref="B1:O1"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="E5:E57"/>
@@ -18551,6 +18506,51 @@
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="N7:O7"/>
     <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="P11:Q11"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B10" xr:uid="{F82E15B8-D06A-4152-8A77-8AE50325986B}">
@@ -25072,6 +25072,9 @@
       <c r="A11" t="s">
         <v>262</v>
       </c>
+      <c r="B11" t="s">
+        <v>1305</v>
+      </c>
       <c r="E11" s="52"/>
       <c r="G11" s="16"/>
       <c r="H11" s="16"/>
@@ -25087,7 +25090,7 @@
         <v>263</v>
       </c>
       <c r="B12" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
       <c r="E12" s="52"/>
       <c r="F12" s="22"/>
@@ -25101,9 +25104,6 @@
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>264</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1302</v>
       </c>
       <c r="E13" s="52"/>
     </row>
@@ -32567,6 +32567,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B1:O1"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="E5:E57"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="H5:N5"/>
     <mergeCell ref="P6:Q6"/>
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="T6:U6"/>
@@ -32576,14 +32584,6 @@
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="L6:M6"/>
     <mergeCell ref="N6:O6"/>
-    <mergeCell ref="B1:O1"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="E5:E57"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="H5:N5"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P4:U4" xr:uid="{0EF314E6-73BE-48BA-8EA7-0A11DA3A5308}">
@@ -74520,15 +74520,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="70db5d92-cf7a-41c9-a808-9efa4eb812f2">
@@ -74539,7 +74530,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005E06BBCF48891B4AA000B842D02367CE" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fe6ea1b7fa6cedb1acda08ea4d5bc607">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="70db5d92-cf7a-41c9-a808-9efa4eb812f2" xmlns:ns3="be71ce3a-ef61-410b-aae3-59cf01e8169d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6c75d4e196960d1be8fe94f46d8363ec" ns2:_="" ns3:_="">
     <xsd:import namespace="70db5d92-cf7a-41c9-a808-9efa4eb812f2"/>
@@ -74740,15 +74731,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B32976BB-D998-4BA5-BBBA-603A232D7A40}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5179601-D499-4F72-B04B-030712A0A5FF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -74765,7 +74757,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F22F824-927F-48AC-8EEE-0CBA7B354FB8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -74782,4 +74774,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B32976BB-D998-4BA5-BBBA-603A232D7A40}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>